--- a/packages/preview/jiangcai-jufe-master-thesis/0.1.1/template/tables/三线表格式说明.xlsx
+++ b/packages/preview/jiangcai-jufe-master-thesis/0.1.1/template/tables/三线表格式说明.xlsx
@@ -43,7 +43,7 @@
     <t xml:space="preserve">表内文字</t>
   </si>
   <si>
-    <t xml:space="preserve">五号字，内容以单行为限</t>
+    <t xml:space="preserve">五号字，行高缺省固定</t>
   </si>
   <si>
     <t xml:space="preserve">跨页续表</t>
